--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\ASAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F110412-601C-4C63-9388-73FE06897336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57E5E38-E669-4652-9948-4B165ED07B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8642,7 +8642,7 @@
         <v>46176.472685185188</v>
       </c>
       <c r="J300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K300" t="s">
         <v>11</v>
@@ -8671,7 +8671,7 @@
         <v>46176.472685185188</v>
       </c>
       <c r="J301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K301" t="s">
         <v>11</v>
@@ -8729,7 +8729,7 @@
         <v>46176.473379629628</v>
       </c>
       <c r="J303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K303" t="s">
         <v>11</v>
@@ -8758,7 +8758,7 @@
         <v>46176.473379629628</v>
       </c>
       <c r="J304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K304" t="s">
         <v>11</v>
@@ -8787,7 +8787,7 @@
         <v>46176.474074074074</v>
       </c>
       <c r="J305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K305" t="s">
         <v>11</v>
@@ -8845,7 +8845,7 @@
         <v>46176.474768518521</v>
       </c>
       <c r="J307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K307" t="s">
         <v>11</v>
@@ -8874,7 +8874,7 @@
         <v>46176.474768518521</v>
       </c>
       <c r="J308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K308" t="s">
         <v>11</v>
@@ -8903,7 +8903,7 @@
         <v>46176.474768518521</v>
       </c>
       <c r="J309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K309" t="s">
         <v>11</v>
@@ -8932,7 +8932,7 @@
         <v>46176.475462962961</v>
       </c>
       <c r="J310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K310" t="s">
         <v>11</v>
@@ -8961,7 +8961,7 @@
         <v>46176.475462962961</v>
       </c>
       <c r="J311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K311" t="s">
         <v>11</v>
@@ -9027,7 +9027,7 @@
         <v>46176.476157407407</v>
       </c>
       <c r="J314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K314" t="s">
         <v>11</v>
@@ -9047,16 +9047,16 @@
         <v>26</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H315" s="2">
-        <v>0</v>
+        <v>8.1365740740740738E-3</v>
       </c>
       <c r="I315" s="1">
         <v>46176.460995370369</v>
       </c>
       <c r="J315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K315" t="s">
         <v>11</v>
@@ -9085,7 +9085,7 @@
         <v>46176.460995370369</v>
       </c>
       <c r="J316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K316" t="s">
         <v>11</v>
@@ -9114,7 +9114,7 @@
         <v>46176.461689814816</v>
       </c>
       <c r="J317">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K317" t="s">
         <v>11</v>
@@ -9143,7 +9143,7 @@
         <v>46176.461689814816</v>
       </c>
       <c r="J318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K318" t="s">
         <v>11</v>
@@ -9172,7 +9172,7 @@
         <v>46176.462384259263</v>
       </c>
       <c r="J319">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K319" t="s">
         <v>11</v>
@@ -9201,7 +9201,7 @@
         <v>46176.462384259263</v>
       </c>
       <c r="J320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K320" t="s">
         <v>11</v>
@@ -9230,7 +9230,7 @@
         <v>46176.463078703702</v>
       </c>
       <c r="J321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K321" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\ASAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AD4FDD7-1BD0-48AA-BB00-4D3BF82DD726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB44C015-8CB9-4AB9-8A52-6DD76FEDCA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="63">
   <si>
     <t>Company Name</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
@@ -598,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -647,13 +650,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>3464</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>20</v>
@@ -676,13 +679,13 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>3453</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>20</v>
@@ -705,13 +708,13 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>3444</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
@@ -734,13 +737,13 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>3470</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>20</v>
@@ -763,13 +766,13 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>3441</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
@@ -796,18 +799,18 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>3457</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
@@ -830,13 +833,13 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>3460</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
@@ -859,13 +862,13 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>3461</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
@@ -888,13 +891,13 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>3407</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
@@ -917,16 +920,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>3468</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
@@ -950,21 +953,21 @@
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>3467</v>
       </c>
       <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -984,16 +987,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15">
         <v>3443</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1013,16 +1016,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16">
         <v>3459</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1042,16 +1045,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17">
         <v>3463</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>12</v>
@@ -1075,21 +1078,21 @@
       <c r="J18" s="2"/>
       <c r="K18" s="1"/>
       <c r="M18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>3469</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>12</v>
@@ -1113,21 +1116,21 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21">
         <v>3458</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1148,24 +1151,23 @@
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23">
         <v>3465</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1185,16 +1187,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24">
         <v>3455</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>12</v>
@@ -1218,21 +1220,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26">
         <v>3448</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1252,16 +1254,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27">
         <v>3466</v>
       </c>
       <c r="F27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1281,16 +1283,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28">
         <v>3442</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>14</v>
@@ -1314,21 +1316,21 @@
       <c r="J29" s="2"/>
       <c r="K29" s="1"/>
       <c r="M29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <v>3447</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1348,16 +1350,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31">
         <v>3454</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1377,16 +1379,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32">
         <v>3445</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1406,16 +1408,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33">
         <v>3446</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1435,16 +1437,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E34">
         <v>3456</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1464,16 +1466,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E35">
         <v>3435</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1493,16 +1495,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E36">
         <v>3462</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1526,18 +1528,18 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38">
         <v>3464</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>19</v>
@@ -1560,13 +1562,13 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39">
         <v>3453</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>19</v>
@@ -1593,18 +1595,18 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41">
         <v>3444</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>19</v>
@@ -1631,18 +1633,18 @@
       <c r="J42" s="2"/>
       <c r="K42" s="1"/>
       <c r="M42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E43">
         <v>3470</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>19</v>
@@ -1669,18 +1671,18 @@
       <c r="J44" s="2"/>
       <c r="K44" s="1"/>
       <c r="M44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E45">
         <v>3441</v>
       </c>
       <c r="F45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>19</v>
@@ -1703,13 +1705,13 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E46">
         <v>3457</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>19</v>
@@ -1736,18 +1738,18 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48">
         <v>3460</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>19</v>
@@ -1770,13 +1772,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E49">
         <v>3461</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>19</v>
@@ -1799,13 +1801,13 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E50">
         <v>3407</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>19</v>
@@ -1828,16 +1830,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51">
         <v>3468</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>14</v>
@@ -1861,21 +1863,21 @@
       <c r="J52" s="2"/>
       <c r="K52" s="1"/>
       <c r="M52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E53">
         <v>3467</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -1895,16 +1897,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E54">
         <v>3443</v>
       </c>
       <c r="F54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1924,16 +1926,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E55">
         <v>3459</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -1953,16 +1955,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E56">
         <v>3463</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -1982,16 +1984,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E57">
         <v>3469</v>
       </c>
       <c r="F57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>14</v>
@@ -2015,21 +2017,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E59">
         <v>3458</v>
       </c>
       <c r="F59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2049,16 +2051,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E60">
         <v>3465</v>
       </c>
       <c r="F60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2078,16 +2080,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E61">
         <v>3455</v>
       </c>
       <c r="F61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2107,16 +2109,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E62">
         <v>3448</v>
       </c>
       <c r="F62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2136,16 +2138,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E63">
         <v>3466</v>
       </c>
       <c r="F63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2165,16 +2167,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E64">
         <v>3442</v>
       </c>
       <c r="F64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>14</v>
@@ -2198,21 +2200,21 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E66">
         <v>3447</v>
       </c>
       <c r="F66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2232,16 +2234,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E67">
         <v>3454</v>
       </c>
       <c r="F67" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2261,16 +2263,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E68">
         <v>3445</v>
       </c>
       <c r="F68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2290,16 +2292,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E69">
         <v>3446</v>
       </c>
       <c r="F69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>14</v>
@@ -2323,21 +2325,21 @@
       <c r="J70" s="2"/>
       <c r="K70" s="1"/>
       <c r="M70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E71">
         <v>3456</v>
       </c>
       <c r="F71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>13</v>
@@ -2357,16 +2359,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E72">
         <v>3435</v>
       </c>
       <c r="F72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2386,16 +2388,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E73">
         <v>3462</v>
       </c>
       <c r="F73" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2415,16 +2417,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E74">
         <v>3464</v>
       </c>
       <c r="F74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>13</v>
@@ -2444,16 +2446,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E75">
         <v>3453</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2473,16 +2475,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E76">
         <v>3444</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2502,16 +2504,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E77">
         <v>3470</v>
       </c>
       <c r="F77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2531,16 +2533,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E78">
         <v>3441</v>
       </c>
       <c r="F78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2560,16 +2562,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E79">
         <v>3457</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2589,16 +2591,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E80">
         <v>3460</v>
       </c>
       <c r="F80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2618,16 +2620,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E81">
         <v>3461</v>
       </c>
       <c r="F81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2647,16 +2649,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E82">
         <v>3407</v>
       </c>
       <c r="F82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2676,16 +2678,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E83">
         <v>3468</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2705,16 +2707,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E84">
         <v>3467</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2734,16 +2736,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E85">
         <v>3443</v>
       </c>
       <c r="F85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2763,16 +2765,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E86">
         <v>3459</v>
       </c>
       <c r="F86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2792,16 +2794,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87">
         <v>3463</v>
       </c>
       <c r="F87" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -2821,16 +2823,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E88">
         <v>3469</v>
       </c>
       <c r="F88" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>12</v>
@@ -2854,21 +2856,21 @@
       <c r="J89" s="2"/>
       <c r="K89" s="1"/>
       <c r="M89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E90">
         <v>3458</v>
       </c>
       <c r="F90" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2888,16 +2890,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E91">
         <v>3465</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -2917,16 +2919,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E92">
         <v>3455</v>
       </c>
       <c r="F92" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -2946,16 +2948,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E93">
         <v>3448</v>
       </c>
       <c r="F93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -2975,16 +2977,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94">
         <v>3466</v>
       </c>
       <c r="F94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3004,16 +3006,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E95">
         <v>3442</v>
       </c>
       <c r="F95" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>13</v>
@@ -3033,16 +3035,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E96">
         <v>3447</v>
       </c>
       <c r="F96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3062,16 +3064,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E97">
         <v>3454</v>
       </c>
       <c r="F97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3091,16 +3093,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E98">
         <v>3445</v>
       </c>
       <c r="F98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3120,16 +3122,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E99">
         <v>3446</v>
       </c>
       <c r="F99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3149,16 +3151,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E100">
         <v>3456</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3178,16 +3180,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E101">
         <v>3435</v>
       </c>
       <c r="F101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3207,16 +3209,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E102">
         <v>3462</v>
       </c>
       <c r="F102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3236,13 +3238,13 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E103">
         <v>3464</v>
       </c>
       <c r="F103" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>16</v>
@@ -3265,13 +3267,13 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E104">
         <v>3453</v>
       </c>
       <c r="F104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>16</v>
@@ -3294,13 +3296,13 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E105">
         <v>3444</v>
       </c>
       <c r="F105" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>16</v>
@@ -3323,13 +3325,13 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E106">
         <v>3470</v>
       </c>
       <c r="F106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>16</v>
@@ -3352,13 +3354,13 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E107">
         <v>3441</v>
       </c>
       <c r="F107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>16</v>
@@ -3381,13 +3383,13 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E108">
         <v>3457</v>
       </c>
       <c r="F108" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>16</v>
@@ -3410,13 +3412,13 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E109">
         <v>3460</v>
       </c>
       <c r="F109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>16</v>
@@ -3439,13 +3441,13 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E110">
         <v>3461</v>
       </c>
       <c r="F110" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>16</v>
@@ -3468,13 +3470,13 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E111">
         <v>3407</v>
       </c>
       <c r="F111" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>16</v>
@@ -3497,16 +3499,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E112">
         <v>3468</v>
       </c>
       <c r="F112" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3526,16 +3528,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E113">
         <v>3467</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3555,16 +3557,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E114">
         <v>3443</v>
       </c>
       <c r="F114" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3584,16 +3586,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E115">
         <v>3459</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3613,16 +3615,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E116">
         <v>3463</v>
       </c>
       <c r="F116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>14</v>
@@ -3646,21 +3648,21 @@
       <c r="J117" s="2"/>
       <c r="K117" s="1"/>
       <c r="M117" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E118">
         <v>3469</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>12</v>
@@ -3684,21 +3686,21 @@
       <c r="J119" s="2"/>
       <c r="K119" s="1"/>
       <c r="M119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E120">
         <v>3458</v>
       </c>
       <c r="F120" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3718,16 +3720,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E121">
         <v>3465</v>
       </c>
       <c r="F121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3747,16 +3749,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E122">
         <v>3455</v>
       </c>
       <c r="F122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -3776,16 +3778,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E123">
         <v>3448</v>
       </c>
       <c r="F123" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3805,16 +3807,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>3466</v>
       </c>
       <c r="F124" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3834,16 +3836,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E125">
         <v>3442</v>
       </c>
       <c r="F125" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3863,16 +3865,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E126">
         <v>3447</v>
       </c>
       <c r="F126" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>13</v>
@@ -3892,16 +3894,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E127">
         <v>3454</v>
       </c>
       <c r="F127" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -3921,16 +3923,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E128">
         <v>3445</v>
       </c>
       <c r="F128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -3950,16 +3952,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E129">
         <v>3446</v>
       </c>
       <c r="F129" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -3979,16 +3981,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E130">
         <v>3456</v>
       </c>
       <c r="F130" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4008,16 +4010,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E131">
         <v>3435</v>
       </c>
       <c r="F131" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4037,16 +4039,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E132">
         <v>3462</v>
       </c>
       <c r="F132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4066,13 +4068,13 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E133">
         <v>3464</v>
       </c>
       <c r="F133" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>17</v>
@@ -4095,13 +4097,13 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E134">
         <v>3468</v>
       </c>
       <c r="F134" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>17</v>
@@ -4124,13 +4126,13 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E135">
         <v>3467</v>
       </c>
       <c r="F135" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>17</v>
@@ -4153,13 +4155,13 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E136">
         <v>3443</v>
       </c>
       <c r="F136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>17</v>
@@ -4182,13 +4184,13 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E137">
         <v>3459</v>
       </c>
       <c r="F137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>17</v>
@@ -4211,13 +4213,13 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E138">
         <v>3463</v>
       </c>
       <c r="F138" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>17</v>
@@ -4240,13 +4242,13 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E139">
         <v>3453</v>
       </c>
       <c r="F139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>17</v>
@@ -4269,13 +4271,13 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E140">
         <v>3469</v>
       </c>
       <c r="F140" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>17</v>
@@ -4298,13 +4300,13 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E141">
         <v>3444</v>
       </c>
       <c r="F141" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>17</v>
@@ -4327,13 +4329,13 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E142">
         <v>3470</v>
       </c>
       <c r="F142" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>17</v>
@@ -4356,13 +4358,13 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E143">
         <v>3458</v>
       </c>
       <c r="F143" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>17</v>
@@ -4385,13 +4387,13 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E144">
         <v>3465</v>
       </c>
       <c r="F144" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>17</v>
@@ -4414,13 +4416,13 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E145">
         <v>3441</v>
       </c>
       <c r="F145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>17</v>
@@ -4443,13 +4445,13 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E146">
         <v>3455</v>
       </c>
       <c r="F146" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>17</v>
@@ -4472,13 +4474,13 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E147">
         <v>3448</v>
       </c>
       <c r="F147" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>17</v>
@@ -4501,13 +4503,13 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E148">
         <v>3466</v>
       </c>
       <c r="F148" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>17</v>
@@ -4530,13 +4532,13 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E149">
         <v>3442</v>
       </c>
       <c r="F149" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>17</v>
@@ -4559,13 +4561,13 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E150">
         <v>3457</v>
       </c>
       <c r="F150" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>17</v>
@@ -4588,13 +4590,13 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E151">
         <v>3447</v>
       </c>
       <c r="F151" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>17</v>
@@ -4617,13 +4619,13 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E152">
         <v>3454</v>
       </c>
       <c r="F152" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>17</v>
@@ -4646,13 +4648,13 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E153">
         <v>3445</v>
       </c>
       <c r="F153" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>17</v>
@@ -4675,13 +4677,13 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E154">
         <v>3446</v>
       </c>
       <c r="F154" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>17</v>
@@ -4704,13 +4706,13 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E155">
         <v>3456</v>
       </c>
       <c r="F155" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>17</v>
@@ -4733,13 +4735,13 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E156">
         <v>3435</v>
       </c>
       <c r="F156" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>17</v>
@@ -4762,13 +4764,13 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E157">
         <v>3460</v>
       </c>
       <c r="F157" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>17</v>
@@ -4791,13 +4793,13 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E158">
         <v>3461</v>
       </c>
       <c r="F158" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>17</v>
@@ -4820,13 +4822,13 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E159">
         <v>3462</v>
       </c>
       <c r="F159" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>17</v>
@@ -4849,13 +4851,13 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E160">
         <v>3407</v>
       </c>
       <c r="F160" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>17</v>
@@ -4878,16 +4880,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E161">
         <v>3468</v>
       </c>
       <c r="F161" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -4907,16 +4909,16 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E162">
         <v>3467</v>
       </c>
       <c r="F162" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -4936,16 +4938,16 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E163">
         <v>3443</v>
       </c>
       <c r="F163" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -4965,16 +4967,16 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E164">
         <v>3459</v>
       </c>
       <c r="F164" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -4994,16 +4996,16 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E165">
         <v>3463</v>
       </c>
       <c r="F165" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5023,16 +5025,16 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E166">
         <v>3469</v>
       </c>
       <c r="F166" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>14</v>
@@ -5056,21 +5058,21 @@
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
       <c r="M167" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E168">
         <v>3444</v>
       </c>
       <c r="F168" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5090,16 +5092,16 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E169">
         <v>3470</v>
       </c>
       <c r="F169" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5119,16 +5121,16 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E170">
         <v>3458</v>
       </c>
       <c r="F170" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>12</v>
@@ -5152,21 +5154,21 @@
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
       <c r="M171" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E172">
         <v>3465</v>
       </c>
       <c r="F172" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>13</v>
@@ -5186,16 +5188,16 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E173">
         <v>3441</v>
       </c>
       <c r="F173" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5215,16 +5217,16 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E174">
         <v>3455</v>
       </c>
       <c r="F174" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5244,16 +5246,16 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E175">
         <v>3448</v>
       </c>
       <c r="F175" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5273,16 +5275,16 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E176">
         <v>3466</v>
       </c>
       <c r="F176" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5302,16 +5304,16 @@
     </row>
     <row r="177" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E177">
         <v>3442</v>
       </c>
       <c r="F177" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5331,16 +5333,16 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E178">
         <v>3457</v>
       </c>
       <c r="F178" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5360,16 +5362,16 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E179">
         <v>3454</v>
       </c>
       <c r="F179" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>12</v>
@@ -5393,21 +5395,21 @@
       <c r="J180" s="2"/>
       <c r="K180" s="1"/>
       <c r="M180" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E181">
         <v>3445</v>
       </c>
       <c r="F181" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5427,16 +5429,16 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E182">
         <v>3446</v>
       </c>
       <c r="F182" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5456,16 +5458,16 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E183">
         <v>3456</v>
       </c>
       <c r="F183" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5485,16 +5487,16 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E184">
         <v>3460</v>
       </c>
       <c r="F184" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5514,16 +5516,16 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E185">
         <v>3462</v>
       </c>
       <c r="F185" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5543,16 +5545,16 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E186">
         <v>3407</v>
       </c>
       <c r="F186" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -5572,16 +5574,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E187">
         <v>3468</v>
       </c>
       <c r="F187" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5601,16 +5603,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E188">
         <v>3467</v>
       </c>
       <c r="F188" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5630,16 +5632,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E189">
         <v>3443</v>
       </c>
       <c r="F189" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5659,16 +5661,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E190">
         <v>3459</v>
       </c>
       <c r="F190" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5688,16 +5690,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E191">
         <v>3463</v>
       </c>
       <c r="F191" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>13</v>
@@ -5717,16 +5719,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E192">
         <v>3469</v>
       </c>
       <c r="F192" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5746,16 +5748,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E193">
         <v>3444</v>
       </c>
       <c r="F193" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5775,16 +5777,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E194">
         <v>3470</v>
       </c>
       <c r="F194" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5804,16 +5806,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E195">
         <v>3458</v>
       </c>
       <c r="F195" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>12</v>
@@ -5837,21 +5839,21 @@
       <c r="J196" s="2"/>
       <c r="K196" s="1"/>
       <c r="M196" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E197">
         <v>3465</v>
       </c>
       <c r="F197" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>13</v>
@@ -5871,16 +5873,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E198">
         <v>3441</v>
       </c>
       <c r="F198" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>13</v>
@@ -5900,16 +5902,16 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E199">
         <v>3455</v>
       </c>
       <c r="F199" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>13</v>
@@ -5929,16 +5931,16 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E200">
         <v>3448</v>
       </c>
       <c r="F200" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>13</v>
@@ -5958,16 +5960,16 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E201">
         <v>3466</v>
       </c>
       <c r="F201" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -5987,16 +5989,16 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E202">
         <v>3442</v>
       </c>
       <c r="F202" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>13</v>
@@ -6016,16 +6018,16 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E203">
         <v>3457</v>
       </c>
       <c r="F203" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6045,16 +6047,16 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E204">
         <v>3454</v>
       </c>
       <c r="F204" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6074,16 +6076,16 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E205">
         <v>3445</v>
       </c>
       <c r="F205" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6103,16 +6105,16 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E206">
         <v>3446</v>
       </c>
       <c r="F206" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>14</v>
@@ -6136,21 +6138,21 @@
       <c r="J207" s="2"/>
       <c r="K207" s="1"/>
       <c r="M207" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E208">
         <v>3456</v>
       </c>
       <c r="F208" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6170,16 +6172,16 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E209">
         <v>3460</v>
       </c>
       <c r="F209" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6199,16 +6201,16 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E210">
         <v>3462</v>
       </c>
       <c r="F210" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6228,16 +6230,16 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E211">
         <v>3407</v>
       </c>
       <c r="F211" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6257,16 +6259,16 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E212">
         <v>3442</v>
       </c>
       <c r="F212" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>14</v>
@@ -6290,21 +6292,21 @@
       <c r="J213" s="2"/>
       <c r="K213" s="1"/>
       <c r="M213" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E214">
         <v>3445</v>
       </c>
       <c r="F214" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6324,16 +6326,16 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E215">
         <v>3442</v>
       </c>
       <c r="F215" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6353,16 +6355,16 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E216">
         <v>3445</v>
       </c>
       <c r="F216" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6382,16 +6384,16 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E217">
         <v>3442</v>
       </c>
       <c r="F217" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6411,16 +6413,16 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E218">
         <v>3445</v>
       </c>
       <c r="F218" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6440,16 +6442,16 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E219">
         <v>3463</v>
       </c>
       <c r="F219" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>14</v>
@@ -6473,21 +6475,21 @@
       <c r="J220" s="2"/>
       <c r="K220" s="1"/>
       <c r="M220" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E221">
         <v>3463</v>
       </c>
       <c r="F221" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>14</v>
@@ -6511,21 +6513,21 @@
       <c r="J222" s="2"/>
       <c r="K222" s="1"/>
       <c r="M222" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E223">
         <v>3463</v>
       </c>
       <c r="F223" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>14</v>
@@ -6549,21 +6551,21 @@
       <c r="J224" s="2"/>
       <c r="K224" s="1"/>
       <c r="M224" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E225">
         <v>3468</v>
       </c>
       <c r="F225" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6583,16 +6585,16 @@
     </row>
     <row r="226" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D226" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E226">
         <v>3467</v>
       </c>
       <c r="F226" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6612,16 +6614,16 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E227">
         <v>3443</v>
       </c>
       <c r="F227" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6641,16 +6643,16 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E228">
         <v>3459</v>
       </c>
       <c r="F228" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6670,16 +6672,16 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E229">
         <v>3463</v>
       </c>
       <c r="F229" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>13</v>
@@ -6699,16 +6701,16 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E230">
         <v>3469</v>
       </c>
       <c r="F230" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>13</v>
@@ -6728,16 +6730,16 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E231">
         <v>3444</v>
       </c>
       <c r="F231" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6757,16 +6759,16 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E232">
         <v>3470</v>
       </c>
       <c r="F232" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -6786,16 +6788,16 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E233">
         <v>3458</v>
       </c>
       <c r="F233" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -6815,16 +6817,16 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E234">
         <v>3465</v>
       </c>
       <c r="F234" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -6844,16 +6846,16 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E235">
         <v>3441</v>
       </c>
       <c r="F235" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -6873,16 +6875,16 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E236">
         <v>3455</v>
       </c>
       <c r="F236" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -6902,16 +6904,16 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E237">
         <v>3448</v>
       </c>
       <c r="F237" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -6931,16 +6933,16 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E238">
         <v>3466</v>
       </c>
       <c r="F238" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -6960,16 +6962,16 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E239">
         <v>3442</v>
       </c>
       <c r="F239" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -6989,16 +6991,16 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E240">
         <v>3457</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>10</v>
@@ -7018,16 +7020,16 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E241">
         <v>3454</v>
       </c>
       <c r="F241" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7047,16 +7049,16 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E242">
         <v>3445</v>
       </c>
       <c r="F242" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7076,16 +7078,16 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E243">
         <v>3446</v>
       </c>
       <c r="F243" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7105,16 +7107,16 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E244">
         <v>3456</v>
       </c>
       <c r="F244" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7134,16 +7136,16 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E245">
         <v>3460</v>
       </c>
       <c r="F245" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7163,16 +7165,16 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E246">
         <v>3462</v>
       </c>
       <c r="F246" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7192,16 +7194,16 @@
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D247" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E247">
         <v>3407</v>
       </c>
       <c r="F247" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7221,16 +7223,16 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E248">
         <v>3468</v>
       </c>
       <c r="F248" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7250,16 +7252,16 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E249">
         <v>3467</v>
       </c>
       <c r="F249" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7279,16 +7281,16 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E250">
         <v>3443</v>
       </c>
       <c r="F250" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>10</v>
@@ -7308,16 +7310,16 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E251">
         <v>3459</v>
       </c>
       <c r="F251" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7337,16 +7339,16 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E252">
         <v>3463</v>
       </c>
       <c r="F252" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7366,16 +7368,16 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E253">
         <v>3469</v>
       </c>
       <c r="F253" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>14</v>
@@ -7399,21 +7401,21 @@
       <c r="J254" s="2"/>
       <c r="K254" s="1"/>
       <c r="M254" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D255" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E255">
         <v>3444</v>
       </c>
       <c r="F255" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7433,16 +7435,16 @@
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E256">
         <v>3470</v>
       </c>
       <c r="F256" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7462,16 +7464,16 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E257">
         <v>3458</v>
       </c>
       <c r="F257" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>13</v>
@@ -7491,16 +7493,16 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E258">
         <v>3465</v>
       </c>
       <c r="F258" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7520,16 +7522,16 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E259">
         <v>3441</v>
       </c>
       <c r="F259" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7549,16 +7551,16 @@
     </row>
     <row r="260" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D260" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E260">
         <v>3455</v>
       </c>
       <c r="F260" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7578,16 +7580,16 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E261">
         <v>3448</v>
       </c>
       <c r="F261" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7607,16 +7609,16 @@
     </row>
     <row r="262" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D262" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E262">
         <v>3466</v>
       </c>
       <c r="F262" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -7636,16 +7638,16 @@
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E263">
         <v>3442</v>
       </c>
       <c r="F263" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -7665,16 +7667,16 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E264">
         <v>3457</v>
       </c>
       <c r="F264" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7694,16 +7696,16 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E265">
         <v>3454</v>
       </c>
       <c r="F265" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7723,16 +7725,16 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E266">
         <v>3445</v>
       </c>
       <c r="F266" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>13</v>
@@ -7752,16 +7754,16 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E267">
         <v>3446</v>
       </c>
       <c r="F267" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -7781,16 +7783,16 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E268">
         <v>3456</v>
       </c>
       <c r="F268" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>12</v>
@@ -7814,21 +7816,21 @@
       <c r="J269" s="2"/>
       <c r="K269" s="1"/>
       <c r="M269" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E270">
         <v>3460</v>
       </c>
       <c r="F270" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -7848,16 +7850,16 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E271">
         <v>3462</v>
       </c>
       <c r="F271" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -7877,16 +7879,16 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E272">
         <v>3407</v>
       </c>
       <c r="F272" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -7906,13 +7908,13 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E273">
         <v>3468</v>
       </c>
       <c r="F273" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>18</v>
@@ -7935,13 +7937,13 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E274">
         <v>3467</v>
       </c>
       <c r="F274" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>18</v>
@@ -7964,13 +7966,13 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E275">
         <v>3443</v>
       </c>
       <c r="F275" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>18</v>
@@ -7993,13 +7995,13 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E276">
         <v>3459</v>
       </c>
       <c r="F276" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>18</v>
@@ -8022,13 +8024,13 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E277">
         <v>3463</v>
       </c>
       <c r="F277" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>18</v>
@@ -8051,13 +8053,13 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E278">
         <v>3469</v>
       </c>
       <c r="F278" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>18</v>
@@ -8084,18 +8086,18 @@
       <c r="J279" s="2"/>
       <c r="K279" s="1"/>
       <c r="M279" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E280">
         <v>3444</v>
       </c>
       <c r="F280" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>18</v>
@@ -8118,13 +8120,13 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E281">
         <v>3470</v>
       </c>
       <c r="F281" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>18</v>
@@ -8147,13 +8149,13 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E282">
         <v>3458</v>
       </c>
       <c r="F282" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>18</v>
@@ -8176,13 +8178,13 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E283">
         <v>3465</v>
       </c>
       <c r="F283" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>18</v>
@@ -8205,13 +8207,13 @@
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E284">
         <v>3441</v>
       </c>
       <c r="F284" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>18</v>
@@ -8234,13 +8236,13 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E285">
         <v>3455</v>
       </c>
       <c r="F285" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>18</v>
@@ -8263,13 +8265,13 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E286">
         <v>3448</v>
       </c>
       <c r="F286" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>18</v>
@@ -8292,13 +8294,13 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E287">
         <v>3466</v>
       </c>
       <c r="F287" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>18</v>
@@ -8321,13 +8323,13 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E288">
         <v>3442</v>
       </c>
       <c r="F288" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>18</v>
@@ -8350,13 +8352,13 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E289">
         <v>3457</v>
       </c>
       <c r="F289" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>18</v>
@@ -8383,18 +8385,18 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E291">
         <v>3454</v>
       </c>
       <c r="F291" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>18</v>
@@ -8417,13 +8419,13 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E292">
         <v>3445</v>
       </c>
       <c r="F292" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>18</v>
@@ -8446,13 +8448,13 @@
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D293" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E293">
         <v>3446</v>
       </c>
       <c r="F293" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>18</v>
@@ -8475,13 +8477,13 @@
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E294">
         <v>3456</v>
       </c>
       <c r="F294" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>18</v>
@@ -8504,13 +8506,13 @@
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E295">
         <v>3460</v>
       </c>
       <c r="F295" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>18</v>
@@ -8537,18 +8539,18 @@
       <c r="J296" s="2"/>
       <c r="K296" s="1"/>
       <c r="M296" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E297">
         <v>3462</v>
       </c>
       <c r="F297" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>18</v>
@@ -8571,13 +8573,13 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E298">
         <v>3407</v>
       </c>
       <c r="F298" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>18</v>
@@ -8600,13 +8602,13 @@
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D299" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E299">
         <v>3444</v>
       </c>
       <c r="F299" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -8629,16 +8631,16 @@
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E300">
         <v>3468</v>
       </c>
       <c r="F300" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8658,16 +8660,16 @@
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D301" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E301">
         <v>3467</v>
       </c>
       <c r="F301" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -8687,16 +8689,16 @@
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E302">
         <v>3443</v>
       </c>
       <c r="F302" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8716,16 +8718,16 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E303">
         <v>3459</v>
       </c>
       <c r="F303" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -8745,16 +8747,16 @@
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D304" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E304">
         <v>3463</v>
       </c>
       <c r="F304" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -8774,16 +8776,16 @@
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E305">
         <v>3469</v>
       </c>
       <c r="F305" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>13</v>
@@ -8803,16 +8805,16 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E306">
         <v>3470</v>
       </c>
       <c r="F306" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8832,16 +8834,16 @@
     </row>
     <row r="307" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D307" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E307">
         <v>3458</v>
       </c>
       <c r="F307" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -8861,16 +8863,16 @@
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E308">
         <v>3465</v>
       </c>
       <c r="F308" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>13</v>
@@ -8890,16 +8892,16 @@
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D309" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E309">
         <v>3441</v>
       </c>
       <c r="F309" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -8919,16 +8921,16 @@
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E310">
         <v>3455</v>
       </c>
       <c r="F310" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -8948,16 +8950,16 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E311">
         <v>3448</v>
       </c>
       <c r="F311" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -8977,16 +8979,16 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E312">
         <v>3466</v>
       </c>
       <c r="F312" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>12</v>
@@ -9010,21 +9012,21 @@
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
       <c r="M313" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E314">
         <v>3442</v>
       </c>
       <c r="F314" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9044,16 +9046,16 @@
     </row>
     <row r="315" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D315" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E315">
         <v>3457</v>
       </c>
       <c r="F315" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -9073,16 +9075,16 @@
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E316">
         <v>3454</v>
       </c>
       <c r="F316" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9102,16 +9104,16 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E317">
         <v>3445</v>
       </c>
       <c r="F317" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>13</v>
@@ -9131,16 +9133,16 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E318">
         <v>3446</v>
       </c>
       <c r="F318" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>13</v>
@@ -9160,16 +9162,16 @@
     </row>
     <row r="319" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D319" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E319">
         <v>3456</v>
       </c>
       <c r="F319" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9189,16 +9191,16 @@
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D320" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E320">
         <v>3460</v>
       </c>
       <c r="F320" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>13</v>
@@ -9218,16 +9220,16 @@
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D321" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E321">
         <v>3462</v>
       </c>
       <c r="F321" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>13</v>
@@ -9247,16 +9249,16 @@
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D322" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E322">
         <v>3407</v>
       </c>
       <c r="F322" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>12</v>
@@ -9280,177 +9282,707 @@
       <c r="J323" s="2"/>
       <c r="K323" s="1"/>
       <c r="M323" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="324" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H324" s="2"/>
-      <c r="I324" s="1"/>
-      <c r="J324" s="2"/>
-      <c r="K324" s="1"/>
+      <c r="D324" t="s">
+        <v>30</v>
+      </c>
+      <c r="E324">
+        <v>3468</v>
+      </c>
+      <c r="F324" t="s">
+        <v>40</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J324" s="2">
+        <v>0</v>
+      </c>
+      <c r="K324" s="1">
+        <v>46213.793749999997</v>
+      </c>
+      <c r="L324">
+        <v>0</v>
+      </c>
+      <c r="M324" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="325" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H325" s="2"/>
-      <c r="I325" s="1"/>
-      <c r="J325" s="2"/>
-      <c r="K325" s="1"/>
+      <c r="D325" t="s">
+        <v>30</v>
+      </c>
+      <c r="E325">
+        <v>3467</v>
+      </c>
+      <c r="F325" t="s">
+        <v>42</v>
+      </c>
+      <c r="H325" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I325" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J325" s="2">
+        <v>0</v>
+      </c>
+      <c r="K325" s="1">
+        <v>46213.794444444444</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+      <c r="M325" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H326" s="2"/>
-      <c r="I326" s="1"/>
-      <c r="K326" s="1"/>
+      <c r="D326" t="s">
+        <v>30</v>
+      </c>
+      <c r="E326">
+        <v>3443</v>
+      </c>
+      <c r="F326" t="s">
+        <v>43</v>
+      </c>
+      <c r="H326" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I326" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326" s="1">
+        <v>46213.795138888891</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+      <c r="M326" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="327" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H327" s="2"/>
-      <c r="I327" s="1"/>
-      <c r="J327" s="2"/>
-      <c r="K327" s="1"/>
+      <c r="D327" t="s">
+        <v>30</v>
+      </c>
+      <c r="E327">
+        <v>3459</v>
+      </c>
+      <c r="F327" t="s">
+        <v>44</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J327" s="2">
+        <v>0</v>
+      </c>
+      <c r="K327" s="1">
+        <v>46213.79583333333</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+      <c r="M327" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H328" s="2"/>
-      <c r="I328" s="1"/>
-      <c r="J328" s="2"/>
-      <c r="K328" s="1"/>
+      <c r="D328" t="s">
+        <v>30</v>
+      </c>
+      <c r="E328">
+        <v>3463</v>
+      </c>
+      <c r="F328" t="s">
+        <v>45</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J328" s="2">
+        <v>0</v>
+      </c>
+      <c r="K328" s="1">
+        <v>46213.79583333333</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+      <c r="M328" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H329" s="2"/>
-      <c r="I329" s="1"/>
-      <c r="J329" s="2"/>
-      <c r="K329" s="1"/>
+      <c r="D329" t="s">
+        <v>30</v>
+      </c>
+      <c r="E329">
+        <v>3469</v>
+      </c>
+      <c r="F329" t="s">
+        <v>46</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J329" s="2">
+        <v>0</v>
+      </c>
+      <c r="K329" s="1">
+        <v>46213.796527777777</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+      <c r="M329" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H330" s="2"/>
-      <c r="I330" s="1"/>
-      <c r="J330" s="2"/>
-      <c r="K330" s="1"/>
+      <c r="D330" t="s">
+        <v>30</v>
+      </c>
+      <c r="E330">
+        <v>3444</v>
+      </c>
+      <c r="F330" t="s">
+        <v>33</v>
+      </c>
+      <c r="H330" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J330" s="2">
+        <v>6.9328703703703705E-3</v>
+      </c>
+      <c r="K330" s="1">
+        <v>46213.797222222223</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+      <c r="M330" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="331" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H331" s="2"/>
-      <c r="I331" s="1"/>
-      <c r="J331" s="2"/>
-      <c r="K331" s="1"/>
+      <c r="D331" t="s">
+        <v>30</v>
+      </c>
+      <c r="E331">
+        <v>3470</v>
+      </c>
+      <c r="F331" t="s">
+        <v>34</v>
+      </c>
+      <c r="H331" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J331" s="2">
+        <v>0</v>
+      </c>
+      <c r="K331" s="1">
+        <v>46213.79791666667</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+      <c r="M331" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H332" s="2"/>
-      <c r="I332" s="1"/>
-      <c r="J332" s="2"/>
-      <c r="K332" s="1"/>
+      <c r="D332" t="s">
+        <v>30</v>
+      </c>
+      <c r="E332">
+        <v>3458</v>
+      </c>
+      <c r="F332" t="s">
+        <v>47</v>
+      </c>
+      <c r="H332" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J332" s="2">
+        <v>0</v>
+      </c>
+      <c r="K332" s="1">
+        <v>46213.79791666667</v>
+      </c>
+      <c r="L332">
+        <v>0</v>
+      </c>
+      <c r="M332" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="333" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H333" s="2"/>
-      <c r="I333" s="1"/>
-      <c r="J333" s="2"/>
-      <c r="K333" s="1"/>
+      <c r="D333" t="s">
+        <v>30</v>
+      </c>
+      <c r="E333">
+        <v>3465</v>
+      </c>
+      <c r="F333" t="s">
+        <v>48</v>
+      </c>
+      <c r="H333" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J333" s="2">
+        <v>0</v>
+      </c>
+      <c r="K333" s="1">
+        <v>46213.798611111109</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H334" s="2"/>
-      <c r="I334" s="1"/>
-      <c r="J334" s="2"/>
-      <c r="K334" s="1"/>
+      <c r="D334" t="s">
+        <v>30</v>
+      </c>
+      <c r="E334">
+        <v>3441</v>
+      </c>
+      <c r="F334" t="s">
+        <v>35</v>
+      </c>
+      <c r="H334" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J334" s="2">
+        <v>0</v>
+      </c>
+      <c r="K334" s="1">
+        <v>46213.799305555556</v>
+      </c>
+      <c r="L334">
+        <v>0</v>
+      </c>
+      <c r="M334" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="335" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H335" s="2"/>
-      <c r="I335" s="1"/>
-      <c r="J335" s="2"/>
-      <c r="K335" s="1"/>
+      <c r="D335" t="s">
+        <v>30</v>
+      </c>
+      <c r="E335">
+        <v>3455</v>
+      </c>
+      <c r="F335" t="s">
+        <v>49</v>
+      </c>
+      <c r="H335" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J335" s="2">
+        <v>0</v>
+      </c>
+      <c r="K335" s="1">
+        <v>46213.8</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+      <c r="M335" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H336" s="2"/>
-      <c r="I336" s="1"/>
-      <c r="J336" s="2"/>
-      <c r="K336" s="1"/>
-    </row>
-    <row r="337" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H337" s="2"/>
-      <c r="I337" s="1"/>
-      <c r="J337" s="2"/>
-      <c r="K337" s="1"/>
-    </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H338" s="2"/>
-      <c r="I338" s="1"/>
-      <c r="J338" s="2"/>
-      <c r="K338" s="1"/>
-    </row>
-    <row r="339" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H339" s="2"/>
-      <c r="I339" s="1"/>
-      <c r="J339" s="2"/>
-      <c r="K339" s="1"/>
-    </row>
-    <row r="340" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H340" s="2"/>
-      <c r="I340" s="1"/>
-      <c r="J340" s="2"/>
-      <c r="K340" s="1"/>
-    </row>
-    <row r="341" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H341" s="2"/>
-      <c r="I341" s="1"/>
-      <c r="J341" s="2"/>
-      <c r="K341" s="1"/>
-    </row>
-    <row r="342" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H342" s="2"/>
-      <c r="I342" s="1"/>
-      <c r="J342" s="2"/>
-      <c r="K342" s="1"/>
-    </row>
-    <row r="343" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H343" s="2"/>
-      <c r="I343" s="1"/>
-      <c r="J343" s="2"/>
-      <c r="K343" s="1"/>
-    </row>
-    <row r="344" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H344" s="2"/>
-      <c r="I344" s="1"/>
-      <c r="J344" s="2"/>
-      <c r="K344" s="1"/>
-    </row>
-    <row r="345" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H345" s="2"/>
-      <c r="I345" s="1"/>
-      <c r="J345" s="2"/>
-      <c r="K345" s="1"/>
-    </row>
-    <row r="346" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H346" s="2"/>
-      <c r="I346" s="1"/>
-      <c r="J346" s="2"/>
-      <c r="K346" s="1"/>
-    </row>
-    <row r="347" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D336" t="s">
+        <v>30</v>
+      </c>
+      <c r="E336">
+        <v>3448</v>
+      </c>
+      <c r="F336" t="s">
+        <v>50</v>
+      </c>
+      <c r="H336" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J336" s="2">
+        <v>0</v>
+      </c>
+      <c r="K336" s="1">
+        <v>46213.8</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="337" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D337" t="s">
+        <v>30</v>
+      </c>
+      <c r="E337">
+        <v>3466</v>
+      </c>
+      <c r="F337" t="s">
+        <v>51</v>
+      </c>
+      <c r="H337" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J337" s="2">
+        <v>0</v>
+      </c>
+      <c r="K337" s="1">
+        <v>46213.800694444442</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+      <c r="M337" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D338" t="s">
+        <v>30</v>
+      </c>
+      <c r="E338">
+        <v>3442</v>
+      </c>
+      <c r="F338" t="s">
+        <v>52</v>
+      </c>
+      <c r="H338" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J338" s="2">
+        <v>0</v>
+      </c>
+      <c r="K338" s="1">
+        <v>46213.801388888889</v>
+      </c>
+      <c r="L338">
+        <v>0</v>
+      </c>
+      <c r="M338" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="339" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D339" t="s">
+        <v>30</v>
+      </c>
+      <c r="E339">
+        <v>3457</v>
+      </c>
+      <c r="F339" t="s">
+        <v>36</v>
+      </c>
+      <c r="H339" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J339" s="2">
+        <v>0</v>
+      </c>
+      <c r="K339" s="1">
+        <v>46213.801388888889</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+      <c r="M339" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D340" t="s">
+        <v>30</v>
+      </c>
+      <c r="E340">
+        <v>3454</v>
+      </c>
+      <c r="F340" t="s">
+        <v>54</v>
+      </c>
+      <c r="H340" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J340" s="2">
+        <v>0</v>
+      </c>
+      <c r="K340" s="1">
+        <v>46213.802083333336</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+      <c r="M340" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="341" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D341" t="s">
+        <v>30</v>
+      </c>
+      <c r="E341">
+        <v>3445</v>
+      </c>
+      <c r="F341" t="s">
+        <v>55</v>
+      </c>
+      <c r="H341" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J341" s="2">
+        <v>0</v>
+      </c>
+      <c r="K341" s="1">
+        <v>46213.802777777775</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D342" t="s">
+        <v>30</v>
+      </c>
+      <c r="E342">
+        <v>3446</v>
+      </c>
+      <c r="F342" t="s">
+        <v>56</v>
+      </c>
+      <c r="H342" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J342" s="2">
+        <v>0</v>
+      </c>
+      <c r="K342" s="1">
+        <v>46213.802777777775</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+      <c r="M342" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="343" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D343" t="s">
+        <v>30</v>
+      </c>
+      <c r="E343">
+        <v>3456</v>
+      </c>
+      <c r="F343" t="s">
+        <v>57</v>
+      </c>
+      <c r="H343" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J343" s="2">
+        <v>0</v>
+      </c>
+      <c r="K343" s="1">
+        <v>46213.803472222222</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+      <c r="M343" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D344" t="s">
+        <v>30</v>
+      </c>
+      <c r="E344">
+        <v>3460</v>
+      </c>
+      <c r="F344" t="s">
+        <v>37</v>
+      </c>
+      <c r="H344" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J344" s="2">
+        <v>0</v>
+      </c>
+      <c r="K344" s="1">
+        <v>46213.804166666669</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+      <c r="M344" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="345" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D345" t="s">
+        <v>30</v>
+      </c>
+      <c r="E345">
+        <v>3462</v>
+      </c>
+      <c r="F345" t="s">
+        <v>59</v>
+      </c>
+      <c r="H345" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J345" s="2">
+        <v>0</v>
+      </c>
+      <c r="K345" s="1">
+        <v>46213.804861111108</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+      <c r="M345" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D346" t="s">
+        <v>30</v>
+      </c>
+      <c r="E346">
+        <v>3407</v>
+      </c>
+      <c r="F346" t="s">
+        <v>39</v>
+      </c>
+      <c r="H346" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J346" s="2">
+        <v>0</v>
+      </c>
+      <c r="K346" s="1">
+        <v>46213.804861111108</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+      <c r="M346" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="347" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H347" s="2"/>
       <c r="I347" s="1"/>
       <c r="J347" s="2"/>
       <c r="K347" s="1"/>
     </row>
-    <row r="348" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H348" s="2"/>
       <c r="I348" s="1"/>
       <c r="J348" s="2"/>
       <c r="K348" s="1"/>
     </row>
-    <row r="349" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H349" s="2"/>
       <c r="I349" s="1"/>
       <c r="J349" s="2"/>
       <c r="K349" s="1"/>
     </row>
-    <row r="350" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H350" s="2"/>
       <c r="I350" s="1"/>
       <c r="J350" s="2"/>
       <c r="K350" s="1"/>
     </row>
-    <row r="351" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H351" s="2"/>
       <c r="I351" s="1"/>
       <c r="J351" s="2"/>
       <c r="K351" s="1"/>
     </row>
-    <row r="352" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H352" s="2"/>
       <c r="I352" s="1"/>
       <c r="J352" s="2"/>
@@ -45675,7 +46207,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\ASAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB44C015-8CB9-4AB9-8A52-6DD76FEDCA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A30F4A2-0949-4A9F-8389-D6F7C6C0B335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,7 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -98,22 +98,25 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Speed Management</t>
+  </si>
+  <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
+    <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
-  </si>
-  <si>
-    <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -122,10 +125,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
+    <t>Scene of an Accident</t>
   </si>
   <si>
-    <t>Scene of an Accident</t>
+    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
   </si>
   <si>
     <t>(Spanish) Scene of an Accident</t>
@@ -601,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -650,13 +653,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>3464</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>20</v>
@@ -679,13 +682,13 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>3453</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>20</v>
@@ -708,13 +711,13 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>3444</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
@@ -737,13 +740,13 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>3470</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>20</v>
@@ -766,13 +769,13 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>3441</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
@@ -799,18 +802,18 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>3457</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
@@ -833,13 +836,13 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9">
         <v>3460</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
@@ -862,13 +865,13 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>3461</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
@@ -891,13 +894,13 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11">
         <v>3407</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
@@ -920,16 +923,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>3468</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
@@ -953,21 +956,21 @@
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14">
         <v>3467</v>
       </c>
       <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -987,16 +990,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>3443</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1016,16 +1019,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16">
         <v>3459</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1045,16 +1048,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17">
         <v>3463</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>12</v>
@@ -1078,21 +1081,21 @@
       <c r="J18" s="2"/>
       <c r="K18" s="1"/>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19">
         <v>3469</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>12</v>
@@ -1116,21 +1119,21 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21">
         <v>3458</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1151,23 +1154,24 @@
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
+      <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23">
         <v>3465</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1187,16 +1191,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24">
         <v>3455</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>12</v>
@@ -1220,21 +1224,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26">
         <v>3448</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1254,16 +1258,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E27">
         <v>3466</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1283,16 +1287,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28">
         <v>3442</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>14</v>
@@ -1316,21 +1320,21 @@
       <c r="J29" s="2"/>
       <c r="K29" s="1"/>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E30">
         <v>3447</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1350,16 +1354,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E31">
         <v>3454</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1379,16 +1383,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E32">
         <v>3445</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1408,16 +1412,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E33">
         <v>3446</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1437,16 +1441,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E34">
         <v>3456</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1466,16 +1470,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E35">
         <v>3435</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1495,16 +1499,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E36">
         <v>3462</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1528,21 +1532,21 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E38">
         <v>3464</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1562,16 +1566,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39">
         <v>3453</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>14</v>
@@ -1595,21 +1599,21 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E41">
         <v>3444</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>14</v>
@@ -1633,21 +1637,21 @@
       <c r="J42" s="2"/>
       <c r="K42" s="1"/>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E43">
         <v>3470</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>12</v>
@@ -1671,21 +1675,21 @@
       <c r="J44" s="2"/>
       <c r="K44" s="1"/>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E45">
         <v>3441</v>
       </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1705,16 +1709,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E46">
         <v>3457</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>12</v>
@@ -1738,21 +1742,21 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E48">
         <v>3460</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1772,16 +1776,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E49">
         <v>3461</v>
       </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1801,16 +1805,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E50">
         <v>3407</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -1830,16 +1834,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E51">
         <v>3468</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>14</v>
@@ -1863,21 +1867,21 @@
       <c r="J52" s="2"/>
       <c r="K52" s="1"/>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E53">
         <v>3467</v>
       </c>
       <c r="F53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -1897,16 +1901,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54">
         <v>3443</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1926,16 +1930,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E55">
         <v>3459</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -1955,16 +1959,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E56">
         <v>3463</v>
       </c>
       <c r="F56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -1984,16 +1988,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E57">
         <v>3469</v>
       </c>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>14</v>
@@ -2017,21 +2021,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E59">
         <v>3458</v>
       </c>
       <c r="F59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2051,16 +2055,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E60">
         <v>3465</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2080,16 +2084,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E61">
         <v>3455</v>
       </c>
       <c r="F61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2109,16 +2113,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E62">
         <v>3448</v>
       </c>
       <c r="F62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2138,16 +2142,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E63">
         <v>3466</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2167,16 +2171,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E64">
         <v>3442</v>
       </c>
       <c r="F64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>14</v>
@@ -2200,21 +2204,21 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E66">
         <v>3447</v>
       </c>
       <c r="F66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2234,16 +2238,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E67">
         <v>3454</v>
       </c>
       <c r="F67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2263,16 +2267,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E68">
         <v>3445</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2292,16 +2296,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E69">
         <v>3446</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>14</v>
@@ -2325,21 +2329,21 @@
       <c r="J70" s="2"/>
       <c r="K70" s="1"/>
       <c r="M70" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E71">
         <v>3456</v>
       </c>
       <c r="F71" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>13</v>
@@ -2359,16 +2363,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E72">
         <v>3435</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2388,16 +2392,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E73">
         <v>3462</v>
       </c>
       <c r="F73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2417,13 +2421,13 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E74">
         <v>3464</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>28</v>
@@ -2446,13 +2450,13 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E75">
         <v>3453</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>28</v>
@@ -2475,13 +2479,13 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E76">
         <v>3444</v>
       </c>
       <c r="F76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>28</v>
@@ -2504,13 +2508,13 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E77">
         <v>3470</v>
       </c>
       <c r="F77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>28</v>
@@ -2533,13 +2537,13 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E78">
         <v>3441</v>
       </c>
       <c r="F78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>28</v>
@@ -2562,13 +2566,13 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E79">
         <v>3457</v>
       </c>
       <c r="F79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>28</v>
@@ -2591,13 +2595,13 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E80">
         <v>3460</v>
       </c>
       <c r="F80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>28</v>
@@ -2620,13 +2624,13 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E81">
         <v>3461</v>
       </c>
       <c r="F81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>28</v>
@@ -2649,13 +2653,13 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E82">
         <v>3407</v>
       </c>
       <c r="F82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>28</v>
@@ -2678,16 +2682,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E83">
         <v>3468</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2707,16 +2711,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E84">
         <v>3467</v>
       </c>
       <c r="F84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2736,16 +2740,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E85">
         <v>3443</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2765,16 +2769,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E86">
         <v>3459</v>
       </c>
       <c r="F86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2794,16 +2798,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E87">
         <v>3463</v>
       </c>
       <c r="F87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -2823,16 +2827,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E88">
         <v>3469</v>
       </c>
       <c r="F88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>12</v>
@@ -2856,21 +2860,21 @@
       <c r="J89" s="2"/>
       <c r="K89" s="1"/>
       <c r="M89" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E90">
         <v>3458</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2890,16 +2894,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E91">
         <v>3465</v>
       </c>
       <c r="F91" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -2919,16 +2923,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E92">
         <v>3455</v>
       </c>
       <c r="F92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -2948,16 +2952,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93">
         <v>3448</v>
       </c>
       <c r="F93" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -2977,16 +2981,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94">
         <v>3466</v>
       </c>
       <c r="F94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3006,16 +3010,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E95">
         <v>3442</v>
       </c>
       <c r="F95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>13</v>
@@ -3035,16 +3039,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96">
         <v>3447</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3064,16 +3068,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E97">
         <v>3454</v>
       </c>
       <c r="F97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3093,16 +3097,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E98">
         <v>3445</v>
       </c>
       <c r="F98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3122,16 +3126,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E99">
         <v>3446</v>
       </c>
       <c r="F99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3151,16 +3155,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E100">
         <v>3456</v>
       </c>
       <c r="F100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3180,16 +3184,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E101">
         <v>3435</v>
       </c>
       <c r="F101" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3209,16 +3213,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E102">
         <v>3462</v>
       </c>
       <c r="F102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3238,13 +3242,13 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E103">
         <v>3464</v>
       </c>
       <c r="F103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>16</v>
@@ -3267,13 +3271,13 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E104">
         <v>3453</v>
       </c>
       <c r="F104" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>16</v>
@@ -3296,13 +3300,13 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E105">
         <v>3444</v>
       </c>
       <c r="F105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>16</v>
@@ -3325,13 +3329,13 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E106">
         <v>3470</v>
       </c>
       <c r="F106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>16</v>
@@ -3354,13 +3358,13 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E107">
         <v>3441</v>
       </c>
       <c r="F107" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>16</v>
@@ -3383,13 +3387,13 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E108">
         <v>3457</v>
       </c>
       <c r="F108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>16</v>
@@ -3412,13 +3416,13 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E109">
         <v>3460</v>
       </c>
       <c r="F109" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>16</v>
@@ -3441,13 +3445,13 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E110">
         <v>3461</v>
       </c>
       <c r="F110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>16</v>
@@ -3470,13 +3474,13 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E111">
         <v>3407</v>
       </c>
       <c r="F111" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>16</v>
@@ -3499,16 +3503,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E112">
         <v>3468</v>
       </c>
       <c r="F112" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3528,16 +3532,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E113">
         <v>3467</v>
       </c>
       <c r="F113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3557,16 +3561,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E114">
         <v>3443</v>
       </c>
       <c r="F114" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3586,16 +3590,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E115">
         <v>3459</v>
       </c>
       <c r="F115" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3615,16 +3619,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E116">
         <v>3463</v>
       </c>
       <c r="F116" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>14</v>
@@ -3648,21 +3652,21 @@
       <c r="J117" s="2"/>
       <c r="K117" s="1"/>
       <c r="M117" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E118">
         <v>3469</v>
       </c>
       <c r="F118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>12</v>
@@ -3686,21 +3690,21 @@
       <c r="J119" s="2"/>
       <c r="K119" s="1"/>
       <c r="M119" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E120">
         <v>3458</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3720,16 +3724,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E121">
         <v>3465</v>
       </c>
       <c r="F121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3749,16 +3753,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E122">
         <v>3455</v>
       </c>
       <c r="F122" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -3778,16 +3782,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E123">
         <v>3448</v>
       </c>
       <c r="F123" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3807,16 +3811,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E124">
         <v>3466</v>
       </c>
       <c r="F124" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3836,16 +3840,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E125">
         <v>3442</v>
       </c>
       <c r="F125" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3865,16 +3869,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E126">
         <v>3447</v>
       </c>
       <c r="F126" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>13</v>
@@ -3894,16 +3898,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E127">
         <v>3454</v>
       </c>
       <c r="F127" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -3923,16 +3927,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E128">
         <v>3445</v>
       </c>
       <c r="F128" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -3952,16 +3956,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E129">
         <v>3446</v>
       </c>
       <c r="F129" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -3981,16 +3985,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E130">
         <v>3456</v>
       </c>
       <c r="F130" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4010,16 +4014,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E131">
         <v>3435</v>
       </c>
       <c r="F131" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4039,16 +4043,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E132">
         <v>3462</v>
       </c>
       <c r="F132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4068,13 +4072,13 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E133">
         <v>3464</v>
       </c>
       <c r="F133" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>17</v>
@@ -4097,13 +4101,13 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E134">
         <v>3468</v>
       </c>
       <c r="F134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>17</v>
@@ -4126,13 +4130,13 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E135">
         <v>3467</v>
       </c>
       <c r="F135" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>17</v>
@@ -4155,13 +4159,13 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E136">
         <v>3443</v>
       </c>
       <c r="F136" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>17</v>
@@ -4184,13 +4188,13 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E137">
         <v>3459</v>
       </c>
       <c r="F137" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>17</v>
@@ -4213,13 +4217,13 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E138">
         <v>3463</v>
       </c>
       <c r="F138" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>17</v>
@@ -4242,13 +4246,13 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E139">
         <v>3453</v>
       </c>
       <c r="F139" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>17</v>
@@ -4271,13 +4275,13 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E140">
         <v>3469</v>
       </c>
       <c r="F140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>17</v>
@@ -4300,13 +4304,13 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E141">
         <v>3444</v>
       </c>
       <c r="F141" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>17</v>
@@ -4329,13 +4333,13 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E142">
         <v>3470</v>
       </c>
       <c r="F142" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>17</v>
@@ -4358,13 +4362,13 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E143">
         <v>3458</v>
       </c>
       <c r="F143" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>17</v>
@@ -4387,13 +4391,13 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E144">
         <v>3465</v>
       </c>
       <c r="F144" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>17</v>
@@ -4416,13 +4420,13 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E145">
         <v>3441</v>
       </c>
       <c r="F145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>17</v>
@@ -4445,13 +4449,13 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E146">
         <v>3455</v>
       </c>
       <c r="F146" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>17</v>
@@ -4474,13 +4478,13 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E147">
         <v>3448</v>
       </c>
       <c r="F147" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>17</v>
@@ -4503,13 +4507,13 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E148">
         <v>3466</v>
       </c>
       <c r="F148" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>17</v>
@@ -4532,13 +4536,13 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E149">
         <v>3442</v>
       </c>
       <c r="F149" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>17</v>
@@ -4561,13 +4565,13 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E150">
         <v>3457</v>
       </c>
       <c r="F150" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>17</v>
@@ -4590,13 +4594,13 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E151">
         <v>3447</v>
       </c>
       <c r="F151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>17</v>
@@ -4619,13 +4623,13 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E152">
         <v>3454</v>
       </c>
       <c r="F152" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>17</v>
@@ -4648,13 +4652,13 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E153">
         <v>3445</v>
       </c>
       <c r="F153" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>17</v>
@@ -4677,13 +4681,13 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E154">
         <v>3446</v>
       </c>
       <c r="F154" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>17</v>
@@ -4706,13 +4710,13 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E155">
         <v>3456</v>
       </c>
       <c r="F155" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>17</v>
@@ -4735,13 +4739,13 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E156">
         <v>3435</v>
       </c>
       <c r="F156" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>17</v>
@@ -4764,13 +4768,13 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E157">
         <v>3460</v>
       </c>
       <c r="F157" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>17</v>
@@ -4793,13 +4797,13 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E158">
         <v>3461</v>
       </c>
       <c r="F158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>17</v>
@@ -4822,13 +4826,13 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E159">
         <v>3462</v>
       </c>
       <c r="F159" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>17</v>
@@ -4851,13 +4855,13 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E160">
         <v>3407</v>
       </c>
       <c r="F160" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>17</v>
@@ -4880,16 +4884,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E161">
         <v>3468</v>
       </c>
       <c r="F161" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -4909,16 +4913,16 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E162">
         <v>3467</v>
       </c>
       <c r="F162" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -4938,16 +4942,16 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E163">
         <v>3443</v>
       </c>
       <c r="F163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -4967,16 +4971,16 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E164">
         <v>3459</v>
       </c>
       <c r="F164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -4996,16 +5000,16 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E165">
         <v>3463</v>
       </c>
       <c r="F165" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5025,16 +5029,16 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E166">
         <v>3469</v>
       </c>
       <c r="F166" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>14</v>
@@ -5058,21 +5062,21 @@
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
       <c r="M167" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E168">
         <v>3444</v>
       </c>
       <c r="F168" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5092,16 +5096,16 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E169">
         <v>3470</v>
       </c>
       <c r="F169" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5121,16 +5125,16 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E170">
         <v>3458</v>
       </c>
       <c r="F170" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>12</v>
@@ -5154,21 +5158,21 @@
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
       <c r="M171" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E172">
         <v>3465</v>
       </c>
       <c r="F172" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>13</v>
@@ -5188,16 +5192,16 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E173">
         <v>3441</v>
       </c>
       <c r="F173" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5217,16 +5221,16 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E174">
         <v>3455</v>
       </c>
       <c r="F174" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5246,16 +5250,16 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E175">
         <v>3448</v>
       </c>
       <c r="F175" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5275,16 +5279,16 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E176">
         <v>3466</v>
       </c>
       <c r="F176" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5304,16 +5308,16 @@
     </row>
     <row r="177" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E177">
         <v>3442</v>
       </c>
       <c r="F177" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5333,16 +5337,16 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E178">
         <v>3457</v>
       </c>
       <c r="F178" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5362,16 +5366,16 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E179">
         <v>3454</v>
       </c>
       <c r="F179" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>12</v>
@@ -5395,21 +5399,21 @@
       <c r="J180" s="2"/>
       <c r="K180" s="1"/>
       <c r="M180" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E181">
         <v>3445</v>
       </c>
       <c r="F181" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5429,16 +5433,16 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E182">
         <v>3446</v>
       </c>
       <c r="F182" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5458,16 +5462,16 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E183">
         <v>3456</v>
       </c>
       <c r="F183" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5487,16 +5491,16 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E184">
         <v>3460</v>
       </c>
       <c r="F184" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5516,16 +5520,16 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E185">
         <v>3462</v>
       </c>
       <c r="F185" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5545,16 +5549,16 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E186">
         <v>3407</v>
       </c>
       <c r="F186" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -5574,16 +5578,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E187">
         <v>3468</v>
       </c>
       <c r="F187" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5603,16 +5607,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E188">
         <v>3467</v>
       </c>
       <c r="F188" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5632,16 +5636,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E189">
         <v>3443</v>
       </c>
       <c r="F189" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5661,16 +5665,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E190">
         <v>3459</v>
       </c>
       <c r="F190" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5690,16 +5694,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E191">
         <v>3463</v>
       </c>
       <c r="F191" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>13</v>
@@ -5719,16 +5723,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E192">
         <v>3469</v>
       </c>
       <c r="F192" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5748,16 +5752,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E193">
         <v>3444</v>
       </c>
       <c r="F193" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5777,16 +5781,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E194">
         <v>3470</v>
       </c>
       <c r="F194" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5806,16 +5810,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E195">
         <v>3458</v>
       </c>
       <c r="F195" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>12</v>
@@ -5839,21 +5843,21 @@
       <c r="J196" s="2"/>
       <c r="K196" s="1"/>
       <c r="M196" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E197">
         <v>3465</v>
       </c>
       <c r="F197" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>13</v>
@@ -5873,16 +5877,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E198">
         <v>3441</v>
       </c>
       <c r="F198" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>13</v>
@@ -5902,16 +5906,16 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E199">
         <v>3455</v>
       </c>
       <c r="F199" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>13</v>
@@ -5931,16 +5935,16 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E200">
         <v>3448</v>
       </c>
       <c r="F200" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>13</v>
@@ -5960,16 +5964,16 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E201">
         <v>3466</v>
       </c>
       <c r="F201" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -5989,16 +5993,16 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E202">
         <v>3442</v>
       </c>
       <c r="F202" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>13</v>
@@ -6018,16 +6022,16 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E203">
         <v>3457</v>
       </c>
       <c r="F203" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6047,16 +6051,16 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E204">
         <v>3454</v>
       </c>
       <c r="F204" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6076,16 +6080,16 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E205">
         <v>3445</v>
       </c>
       <c r="F205" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6105,16 +6109,16 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E206">
         <v>3446</v>
       </c>
       <c r="F206" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>14</v>
@@ -6138,21 +6142,21 @@
       <c r="J207" s="2"/>
       <c r="K207" s="1"/>
       <c r="M207" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E208">
         <v>3456</v>
       </c>
       <c r="F208" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6172,16 +6176,16 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E209">
         <v>3460</v>
       </c>
       <c r="F209" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6201,16 +6205,16 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E210">
         <v>3462</v>
       </c>
       <c r="F210" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6230,16 +6234,16 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E211">
         <v>3407</v>
       </c>
       <c r="F211" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6259,16 +6263,16 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E212">
         <v>3442</v>
       </c>
       <c r="F212" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>14</v>
@@ -6292,21 +6296,21 @@
       <c r="J213" s="2"/>
       <c r="K213" s="1"/>
       <c r="M213" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E214">
         <v>3445</v>
       </c>
       <c r="F214" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6326,16 +6330,16 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E215">
         <v>3442</v>
       </c>
       <c r="F215" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6355,16 +6359,16 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E216">
         <v>3445</v>
       </c>
       <c r="F216" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6384,16 +6388,16 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E217">
         <v>3442</v>
       </c>
       <c r="F217" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6413,16 +6417,16 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E218">
         <v>3445</v>
       </c>
       <c r="F218" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6442,16 +6446,16 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E219">
         <v>3463</v>
       </c>
       <c r="F219" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>14</v>
@@ -6475,21 +6479,21 @@
       <c r="J220" s="2"/>
       <c r="K220" s="1"/>
       <c r="M220" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E221">
         <v>3463</v>
       </c>
       <c r="F221" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>14</v>
@@ -6513,21 +6517,21 @@
       <c r="J222" s="2"/>
       <c r="K222" s="1"/>
       <c r="M222" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E223">
         <v>3463</v>
       </c>
       <c r="F223" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>14</v>
@@ -6551,21 +6555,21 @@
       <c r="J224" s="2"/>
       <c r="K224" s="1"/>
       <c r="M224" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E225">
         <v>3468</v>
       </c>
       <c r="F225" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6585,16 +6589,16 @@
     </row>
     <row r="226" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D226" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E226">
         <v>3467</v>
       </c>
       <c r="F226" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6614,16 +6618,16 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E227">
         <v>3443</v>
       </c>
       <c r="F227" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6643,16 +6647,16 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E228">
         <v>3459</v>
       </c>
       <c r="F228" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6672,16 +6676,16 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E229">
         <v>3463</v>
       </c>
       <c r="F229" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>13</v>
@@ -6701,16 +6705,16 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E230">
         <v>3469</v>
       </c>
       <c r="F230" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>13</v>
@@ -6730,16 +6734,16 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E231">
         <v>3444</v>
       </c>
       <c r="F231" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -6759,16 +6763,16 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E232">
         <v>3470</v>
       </c>
       <c r="F232" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -6788,16 +6792,16 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E233">
         <v>3458</v>
       </c>
       <c r="F233" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -6817,16 +6821,16 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E234">
         <v>3465</v>
       </c>
       <c r="F234" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -6846,16 +6850,16 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E235">
         <v>3441</v>
       </c>
       <c r="F235" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -6875,16 +6879,16 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E236">
         <v>3455</v>
       </c>
       <c r="F236" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -6904,16 +6908,16 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E237">
         <v>3448</v>
       </c>
       <c r="F237" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -6933,16 +6937,16 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E238">
         <v>3466</v>
       </c>
       <c r="F238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -6962,16 +6966,16 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E239">
         <v>3442</v>
       </c>
       <c r="F239" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -6991,16 +6995,16 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E240">
         <v>3457</v>
       </c>
       <c r="F240" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>10</v>
@@ -7020,16 +7024,16 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E241">
         <v>3454</v>
       </c>
       <c r="F241" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7049,16 +7053,16 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E242">
         <v>3445</v>
       </c>
       <c r="F242" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7078,16 +7082,16 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E243">
         <v>3446</v>
       </c>
       <c r="F243" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7107,16 +7111,16 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E244">
         <v>3456</v>
       </c>
       <c r="F244" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7136,16 +7140,16 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E245">
         <v>3460</v>
       </c>
       <c r="F245" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7165,16 +7169,16 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E246">
         <v>3462</v>
       </c>
       <c r="F246" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7194,16 +7198,16 @@
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D247" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E247">
         <v>3407</v>
       </c>
       <c r="F247" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7223,16 +7227,16 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E248">
         <v>3468</v>
       </c>
       <c r="F248" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7252,16 +7256,16 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E249">
         <v>3467</v>
       </c>
       <c r="F249" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7281,16 +7285,16 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E250">
         <v>3443</v>
       </c>
       <c r="F250" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>10</v>
@@ -7310,16 +7314,16 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E251">
         <v>3459</v>
       </c>
       <c r="F251" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7339,16 +7343,16 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E252">
         <v>3463</v>
       </c>
       <c r="F252" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7368,16 +7372,16 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E253">
         <v>3469</v>
       </c>
       <c r="F253" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>14</v>
@@ -7401,21 +7405,21 @@
       <c r="J254" s="2"/>
       <c r="K254" s="1"/>
       <c r="M254" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="255" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D255" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E255">
         <v>3444</v>
       </c>
       <c r="F255" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7435,16 +7439,16 @@
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E256">
         <v>3470</v>
       </c>
       <c r="F256" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7464,16 +7468,16 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E257">
         <v>3458</v>
       </c>
       <c r="F257" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>13</v>
@@ -7493,16 +7497,16 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E258">
         <v>3465</v>
       </c>
       <c r="F258" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7522,16 +7526,16 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E259">
         <v>3441</v>
       </c>
       <c r="F259" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7551,16 +7555,16 @@
     </row>
     <row r="260" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D260" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E260">
         <v>3455</v>
       </c>
       <c r="F260" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7580,16 +7584,16 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E261">
         <v>3448</v>
       </c>
       <c r="F261" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7609,16 +7613,16 @@
     </row>
     <row r="262" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D262" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E262">
         <v>3466</v>
       </c>
       <c r="F262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -7638,16 +7642,16 @@
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E263">
         <v>3442</v>
       </c>
       <c r="F263" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -7667,16 +7671,16 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E264">
         <v>3457</v>
       </c>
       <c r="F264" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7696,16 +7700,16 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E265">
         <v>3454</v>
       </c>
       <c r="F265" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7725,16 +7729,16 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E266">
         <v>3445</v>
       </c>
       <c r="F266" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>13</v>
@@ -7754,16 +7758,16 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E267">
         <v>3446</v>
       </c>
       <c r="F267" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -7783,16 +7787,16 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E268">
         <v>3456</v>
       </c>
       <c r="F268" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>12</v>
@@ -7816,21 +7820,21 @@
       <c r="J269" s="2"/>
       <c r="K269" s="1"/>
       <c r="M269" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E270">
         <v>3460</v>
       </c>
       <c r="F270" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -7850,16 +7854,16 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E271">
         <v>3462</v>
       </c>
       <c r="F271" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -7879,16 +7883,16 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E272">
         <v>3407</v>
       </c>
       <c r="F272" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -7908,13 +7912,13 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E273">
         <v>3468</v>
       </c>
       <c r="F273" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>18</v>
@@ -7937,13 +7941,13 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E274">
         <v>3467</v>
       </c>
       <c r="F274" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>18</v>
@@ -7966,13 +7970,13 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E275">
         <v>3443</v>
       </c>
       <c r="F275" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>18</v>
@@ -7995,13 +7999,13 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E276">
         <v>3459</v>
       </c>
       <c r="F276" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>18</v>
@@ -8024,13 +8028,13 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E277">
         <v>3463</v>
       </c>
       <c r="F277" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>18</v>
@@ -8053,13 +8057,13 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E278">
         <v>3469</v>
       </c>
       <c r="F278" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>18</v>
@@ -8086,18 +8090,18 @@
       <c r="J279" s="2"/>
       <c r="K279" s="1"/>
       <c r="M279" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E280">
         <v>3444</v>
       </c>
       <c r="F280" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>18</v>
@@ -8120,13 +8124,13 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E281">
         <v>3470</v>
       </c>
       <c r="F281" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>18</v>
@@ -8149,13 +8153,13 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E282">
         <v>3458</v>
       </c>
       <c r="F282" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>18</v>
@@ -8178,13 +8182,13 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E283">
         <v>3465</v>
       </c>
       <c r="F283" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>18</v>
@@ -8207,13 +8211,13 @@
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E284">
         <v>3441</v>
       </c>
       <c r="F284" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>18</v>
@@ -8236,13 +8240,13 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E285">
         <v>3455</v>
       </c>
       <c r="F285" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>18</v>
@@ -8265,13 +8269,13 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E286">
         <v>3448</v>
       </c>
       <c r="F286" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>18</v>
@@ -8294,13 +8298,13 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E287">
         <v>3466</v>
       </c>
       <c r="F287" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>18</v>
@@ -8323,13 +8327,13 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E288">
         <v>3442</v>
       </c>
       <c r="F288" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>18</v>
@@ -8352,13 +8356,13 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E289">
         <v>3457</v>
       </c>
       <c r="F289" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>18</v>
@@ -8385,18 +8389,18 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E291">
         <v>3454</v>
       </c>
       <c r="F291" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>18</v>
@@ -8419,13 +8423,13 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E292">
         <v>3445</v>
       </c>
       <c r="F292" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>18</v>
@@ -8448,13 +8452,13 @@
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D293" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E293">
         <v>3446</v>
       </c>
       <c r="F293" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>18</v>
@@ -8477,13 +8481,13 @@
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E294">
         <v>3456</v>
       </c>
       <c r="F294" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>18</v>
@@ -8506,13 +8510,13 @@
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E295">
         <v>3460</v>
       </c>
       <c r="F295" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>18</v>
@@ -8539,18 +8543,18 @@
       <c r="J296" s="2"/>
       <c r="K296" s="1"/>
       <c r="M296" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E297">
         <v>3462</v>
       </c>
       <c r="F297" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>18</v>
@@ -8573,13 +8577,13 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E298">
         <v>3407</v>
       </c>
       <c r="F298" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>18</v>
@@ -8602,16 +8606,16 @@
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D299" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E299">
         <v>3444</v>
       </c>
       <c r="F299" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8631,16 +8635,16 @@
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E300">
         <v>3468</v>
       </c>
       <c r="F300" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8660,16 +8664,16 @@
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D301" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E301">
         <v>3467</v>
       </c>
       <c r="F301" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -8689,16 +8693,16 @@
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E302">
         <v>3443</v>
       </c>
       <c r="F302" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8718,16 +8722,16 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E303">
         <v>3459</v>
       </c>
       <c r="F303" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -8747,16 +8751,16 @@
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D304" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E304">
         <v>3463</v>
       </c>
       <c r="F304" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -8776,16 +8780,16 @@
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E305">
         <v>3469</v>
       </c>
       <c r="F305" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>13</v>
@@ -8805,16 +8809,16 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E306">
         <v>3470</v>
       </c>
       <c r="F306" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8834,16 +8838,16 @@
     </row>
     <row r="307" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D307" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E307">
         <v>3458</v>
       </c>
       <c r="F307" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -8863,16 +8867,16 @@
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E308">
         <v>3465</v>
       </c>
       <c r="F308" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>13</v>
@@ -8892,16 +8896,16 @@
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D309" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E309">
         <v>3441</v>
       </c>
       <c r="F309" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -8921,16 +8925,16 @@
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E310">
         <v>3455</v>
       </c>
       <c r="F310" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -8950,16 +8954,16 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E311">
         <v>3448</v>
       </c>
       <c r="F311" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -8979,16 +8983,16 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E312">
         <v>3466</v>
       </c>
       <c r="F312" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>12</v>
@@ -9012,21 +9016,21 @@
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
       <c r="M313" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E314">
         <v>3442</v>
       </c>
       <c r="F314" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9046,16 +9050,16 @@
     </row>
     <row r="315" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D315" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E315">
         <v>3457</v>
       </c>
       <c r="F315" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -9075,16 +9079,16 @@
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E316">
         <v>3454</v>
       </c>
       <c r="F316" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9104,16 +9108,16 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E317">
         <v>3445</v>
       </c>
       <c r="F317" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>13</v>
@@ -9133,16 +9137,16 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E318">
         <v>3446</v>
       </c>
       <c r="F318" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>13</v>
@@ -9162,16 +9166,16 @@
     </row>
     <row r="319" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D319" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E319">
         <v>3456</v>
       </c>
       <c r="F319" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9191,16 +9195,16 @@
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D320" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E320">
         <v>3460</v>
       </c>
       <c r="F320" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>13</v>
@@ -9220,16 +9224,16 @@
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D321" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E321">
         <v>3462</v>
       </c>
       <c r="F321" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>13</v>
@@ -9249,16 +9253,16 @@
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D322" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E322">
         <v>3407</v>
       </c>
       <c r="F322" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>12</v>
@@ -9282,21 +9286,21 @@
       <c r="J323" s="2"/>
       <c r="K323" s="1"/>
       <c r="M323" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D324" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E324">
         <v>3468</v>
       </c>
       <c r="F324" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9316,16 +9320,16 @@
     </row>
     <row r="325" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D325" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E325">
         <v>3467</v>
       </c>
       <c r="F325" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9345,21 +9349,21 @@
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D326" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E326">
         <v>3443</v>
       </c>
       <c r="F326" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J326">
+      <c r="J326" s="2">
         <v>0</v>
       </c>
       <c r="K326" s="1">
@@ -9374,16 +9378,16 @@
     </row>
     <row r="327" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D327" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E327">
         <v>3459</v>
       </c>
       <c r="F327" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>13</v>
@@ -9403,16 +9407,16 @@
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D328" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E328">
         <v>3463</v>
       </c>
       <c r="F328" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9432,16 +9436,16 @@
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D329" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E329">
         <v>3469</v>
       </c>
       <c r="F329" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>13</v>
@@ -9461,16 +9465,16 @@
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D330" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E330">
         <v>3444</v>
       </c>
       <c r="F330" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9490,16 +9494,16 @@
     </row>
     <row r="331" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D331" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E331">
         <v>3470</v>
       </c>
       <c r="F331" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>13</v>
@@ -9519,16 +9523,16 @@
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D332" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E332">
         <v>3458</v>
       </c>
       <c r="F332" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9548,16 +9552,16 @@
     </row>
     <row r="333" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D333" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E333">
         <v>3465</v>
       </c>
       <c r="F333" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9577,16 +9581,16 @@
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D334" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E334">
         <v>3441</v>
       </c>
       <c r="F334" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>13</v>
@@ -9606,16 +9610,16 @@
     </row>
     <row r="335" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D335" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E335">
         <v>3455</v>
       </c>
       <c r="F335" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>13</v>
@@ -9635,16 +9639,16 @@
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D336" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E336">
         <v>3448</v>
       </c>
       <c r="F336" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>13</v>
@@ -9664,16 +9668,16 @@
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D337" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E337">
         <v>3466</v>
       </c>
       <c r="F337" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -9693,16 +9697,16 @@
     </row>
     <row r="338" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D338" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E338">
         <v>3442</v>
       </c>
       <c r="F338" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9722,16 +9726,16 @@
     </row>
     <row r="339" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D339" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E339">
         <v>3457</v>
       </c>
       <c r="F339" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>13</v>
@@ -9751,16 +9755,16 @@
     </row>
     <row r="340" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D340" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E340">
         <v>3454</v>
       </c>
       <c r="F340" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>13</v>
@@ -9780,16 +9784,16 @@
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D341" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E341">
         <v>3445</v>
       </c>
       <c r="F341" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -9809,16 +9813,16 @@
     </row>
     <row r="342" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D342" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E342">
         <v>3446</v>
       </c>
       <c r="F342" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9838,16 +9842,16 @@
     </row>
     <row r="343" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D343" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E343">
         <v>3456</v>
       </c>
       <c r="F343" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>13</v>
@@ -9867,16 +9871,16 @@
     </row>
     <row r="344" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D344" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E344">
         <v>3460</v>
       </c>
       <c r="F344" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -9896,16 +9900,16 @@
     </row>
     <row r="345" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D345" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E345">
         <v>3462</v>
       </c>
       <c r="F345" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -9925,22 +9929,22 @@
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D346" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E346">
         <v>3407</v>
       </c>
       <c r="F346" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J346" s="2">
-        <v>0</v>
+        <v>1.0729166666666666E-2</v>
       </c>
       <c r="K346" s="1">
         <v>46213.804861111108</v>
@@ -9953,22 +9957,91 @@
       </c>
     </row>
     <row r="347" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H347" s="2"/>
-      <c r="I347" s="1"/>
-      <c r="J347" s="2"/>
-      <c r="K347" s="1"/>
+      <c r="D347" t="s">
+        <v>31</v>
+      </c>
+      <c r="E347">
+        <v>3443</v>
+      </c>
+      <c r="F347" t="s">
+        <v>44</v>
+      </c>
+      <c r="H347" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J347" s="2">
+        <v>0</v>
+      </c>
+      <c r="K347" s="1">
+        <v>46217.628125000003</v>
+      </c>
+      <c r="L347">
+        <v>0</v>
+      </c>
+      <c r="M347" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="348" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H348" s="2"/>
-      <c r="I348" s="1"/>
-      <c r="J348" s="2"/>
-      <c r="K348" s="1"/>
+      <c r="D348" t="s">
+        <v>31</v>
+      </c>
+      <c r="E348">
+        <v>3463</v>
+      </c>
+      <c r="F348" t="s">
+        <v>46</v>
+      </c>
+      <c r="H348" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J348" s="2">
+        <v>0</v>
+      </c>
+      <c r="K348" s="1">
+        <v>46217.628819444442</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+      <c r="M348" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="349" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H349" s="2"/>
-      <c r="I349" s="1"/>
-      <c r="J349" s="2"/>
-      <c r="K349" s="1"/>
+      <c r="D349" t="s">
+        <v>31</v>
+      </c>
+      <c r="E349">
+        <v>3407</v>
+      </c>
+      <c r="F349" t="s">
+        <v>40</v>
+      </c>
+      <c r="H349" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I349" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J349" s="2">
+        <v>0</v>
+      </c>
+      <c r="K349" s="1">
+        <v>46217.629513888889</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+      <c r="M349" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="350" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H350" s="2"/>
@@ -10141,6 +10214,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -10704,6 +10778,7 @@
     <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
+      <c r="J472" s="2"/>
       <c r="K472" s="1"/>
     </row>
     <row r="473" spans="8:11" x14ac:dyDescent="0.3">
@@ -12052,6 +12127,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -12361,6 +12437,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -12450,6 +12527,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -12556,6 +12634,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -12573,6 +12652,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -12584,6 +12664,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -12625,6 +12706,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -12648,6 +12730,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -12671,6 +12754,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -12688,6 +12772,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -12699,11 +12784,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -12823,6 +12910,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -12906,6 +12994,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -12929,6 +13018,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -12940,6 +13030,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -12951,6 +13042,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -12998,6 +13090,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -13051,6 +13144,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -13223,6 +13317,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -13234,6 +13329,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -13311,6 +13407,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -13328,6 +13425,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -13375,6 +13473,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -13487,6 +13586,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -13546,6 +13646,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -13557,6 +13658,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -13628,6 +13730,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -13680,6 +13783,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -13756,11 +13860,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -13820,6 +13926,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -13831,6 +13938,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -13842,11 +13950,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -13900,6 +14010,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -13916,6 +14027,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -13939,6 +14051,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -13956,6 +14069,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -14002,11 +14116,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -14048,11 +14164,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -14070,6 +14188,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -14081,6 +14200,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -14092,6 +14212,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -14109,6 +14230,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -14186,6 +14308,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -14215,6 +14338,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -14226,16 +14350,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -14247,16 +14374,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -14268,11 +14398,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -14296,6 +14428,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -14337,6 +14470,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -14366,21 +14500,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -14392,6 +14530,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -14409,6 +14548,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -14448,11 +14588,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -14500,6 +14642,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -14529,6 +14672,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -14605,6 +14749,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -14651,6 +14796,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -14686,11 +14832,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -14707,6 +14855,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -14717,6 +14866,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -14752,6 +14902,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -14763,6 +14914,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -14774,6 +14926,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -14785,6 +14938,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -14796,6 +14950,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -14837,6 +14992,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -14854,6 +15010,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -14871,6 +15028,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -14912,6 +15070,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -14935,6 +15094,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -14981,6 +15141,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -15016,6 +15177,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -15039,6 +15201,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -15079,6 +15242,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -15096,11 +15260,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -15159,6 +15325,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -15175,6 +15342,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -15186,6 +15354,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -15197,11 +15366,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -15237,6 +15408,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -15289,6 +15461,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -15299,6 +15472,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -15314,6 +15488,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -15337,16 +15512,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -15417,6 +15595,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -15428,6 +15607,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -15528,6 +15708,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -15584,6 +15766,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -15607,6 +15790,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -15731,6 +15915,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -15889,6 +16074,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -15906,6 +16092,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -15946,6 +16133,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -16278,6 +16466,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -16366,6 +16555,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -16459,6 +16649,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -16518,11 +16709,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -16574,6 +16767,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -16615,6 +16809,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -16659,6 +16854,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -16705,11 +16901,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -16907,6 +17105,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -16936,6 +17135,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -16951,6 +17152,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -17010,6 +17212,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -17081,6 +17284,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -17122,6 +17326,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -17240,6 +17445,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -17304,6 +17510,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -17428,6 +17635,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -17654,6 +17862,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -17771,6 +17980,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -17854,6 +18064,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -17913,6 +18124,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -17936,6 +18148,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -17983,6 +18196,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -18042,6 +18256,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -18065,6 +18280,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -18082,6 +18298,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -18165,6 +18382,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -18356,6 +18574,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -46212,6 +46431,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -46219,6 +46439,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -46226,6 +46447,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -46241,6 +46463,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -46250,6 +46473,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -46257,9 +46481,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -46267,12 +46497,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -46280,12 +46513,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -46297,9 +46533,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -46314,6 +46552,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -46340,6 +46579,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -46350,7 +46590,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -46358,6 +46603,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -46369,6 +46615,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -46376,6 +46623,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -46390,13 +46638,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -46407,15 +46661,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -46431,6 +46688,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -46449,6 +46707,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -46460,6 +46719,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -46477,18 +46737,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -46517,6 +46782,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -46524,9 +46790,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -46549,12 +46817,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -46569,9 +46840,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -46587,12 +46860,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -46613,6 +46888,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -46624,9 +46900,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -46638,6 +46916,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -46677,9 +46956,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -46687,9 +46968,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -46700,6 +46983,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -46707,18 +46991,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -46726,6 +47018,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -46736,6 +47029,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -46762,15 +47056,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -46792,6 +47090,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -46799,9 +47098,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -46809,6 +47110,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -46820,6 +47122,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -46834,6 +47137,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -46843,6 +47150,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -46854,6 +47162,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -46864,10 +47173,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -46875,6 +47189,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -46889,6 +47204,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -46911,6 +47227,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -46930,25 +47247,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -46956,6 +47285,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -46963,15 +47293,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -46985,6 +47322,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -47003,9 +47341,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -47013,9 +47353,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -47023,6 +47365,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -47039,10 +47382,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
